--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5952,6 +5952,4409 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125800234</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>714273</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6395095</v>
+      </c>
+      <c r="S44" t="n">
+        <v>18</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125798802</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>714270</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6395091</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125797908</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>714352</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6394957</v>
+      </c>
+      <c r="S46" t="n">
+        <v>18</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125801883</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>714372</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6395100</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125798096</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>714304</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6395005</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125800049</v>
+      </c>
+      <c r="B49" t="n">
+        <v>105260</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>714240</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6395175</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125802957</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57932</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>714254</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6395049</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125800012</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>714239</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6395154</v>
+      </c>
+      <c r="S51" t="n">
+        <v>18</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125799723</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>714256</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6395124</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125797549</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>714361</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6394936</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125800687</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58128</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102625</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Halsbandsflugsnappare</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ficedula albicollis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>714279</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6395109</v>
+      </c>
+      <c r="S54" t="n">
+        <v>16</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Camilla Edvinsson, Nora Toftgård Shahnavaz, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125799309</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>714260</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6395087</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125801401</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>714326</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6395124</v>
+      </c>
+      <c r="S56" t="n">
+        <v>12</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125799607</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>714256</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6395083</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125799057</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>714316</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6395075</v>
+      </c>
+      <c r="S58" t="n">
+        <v>14</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125798798</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>714270</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6395091</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125800799</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>714298</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6395044</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125801701</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>714318</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6395132</v>
+      </c>
+      <c r="S61" t="n">
+        <v>12</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125798213</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>714315</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6394992</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125798048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>714313</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6395016</v>
+      </c>
+      <c r="S63" t="n">
+        <v>12</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125799922</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>714240</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6395123</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125797646</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>714368</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6394946</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125800259</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>714261</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6395081</v>
+      </c>
+      <c r="S66" t="n">
+        <v>16</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125797584</v>
+      </c>
+      <c r="B67" t="n">
+        <v>110404</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>714345</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6394926</v>
+      </c>
+      <c r="S67" t="n">
+        <v>18</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125799641</v>
+      </c>
+      <c r="B68" t="n">
+        <v>95450</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>714248</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6395081</v>
+      </c>
+      <c r="S68" t="n">
+        <v>16</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125798280</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>714298</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6395026</v>
+      </c>
+      <c r="S69" t="n">
+        <v>8</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125798187</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>714301</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6395029</v>
+      </c>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125814124</v>
+      </c>
+      <c r="B71" t="n">
+        <v>56947</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>714386</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6395050</v>
+      </c>
+      <c r="S71" t="n">
+        <v>50</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125800937</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57664</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>714265</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6395124</v>
+      </c>
+      <c r="S72" t="n">
+        <v>12</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125800859</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>714265</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6395124</v>
+      </c>
+      <c r="S73" t="n">
+        <v>16</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125800830</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58128</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>102625</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Halsbandsflugsnappare</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ficedula albicollis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>714267</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6395077</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125798516</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>714263</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6395090</v>
+      </c>
+      <c r="S75" t="n">
+        <v>11</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125800866</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>714279</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6395120</v>
+      </c>
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125814167</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98347</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>714271</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6395065</v>
+      </c>
+      <c r="S77" t="n">
+        <v>40</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125808000</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stora sojdeby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>714264</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6395004</v>
+      </c>
+      <c r="S78" t="n">
+        <v>9</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125797532</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8361</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>714342</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6394935</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Elis Lewin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125797614</v>
+      </c>
+      <c r="B80" t="n">
+        <v>105908</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>714333</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6394948</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125808001</v>
+      </c>
+      <c r="B81" t="n">
+        <v>85553</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>258917</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hypoxylon petriniae</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stora sojdeby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>714264</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6395004</v>
+      </c>
+      <c r="S81" t="n">
+        <v>9</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125800805</v>
+      </c>
+      <c r="B82" t="n">
+        <v>5166</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100276</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Prydnadsbock</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Anaglyptus mysticus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fole lund, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>714269</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6395114</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Max Karlsson, Malte Lindberg, Alec Bailey, Elvira Klang, Filippa Paperin, Elis Lewin, Emilia Blixt, Ivar Anderberg, Nora Toftgård Shahnavaz, Karl Soler Kinnerbäck, Karin Andersson, Erik Christiansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,46 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125800234</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98302</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6001,10 +5998,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714273</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395095</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
         <v>18</v>
@@ -6036,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6046,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6188,43 +6185,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797908</v>
+        <v>125800234</v>
       </c>
       <c r="B46" t="n">
-        <v>8361</v>
+        <v>98302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106540</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714352</v>
+        <v>714273</v>
       </c>
       <c r="R46" t="n">
-        <v>6394957</v>
+        <v>6395095</v>
       </c>
       <c r="S46" t="n">
         <v>18</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7779,10 +7779,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B60" t="n">
-        <v>91240</v>
+        <v>8361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,30 +7790,32 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7821,13 +7823,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R60" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7856,7 +7858,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7866,7 +7868,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7893,7 +7895,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B61" t="n">
         <v>8447</v>
@@ -7937,10 +7939,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7972,7 +7974,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7982,7 +7984,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8009,10 +8011,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B62" t="n">
-        <v>8361</v>
+        <v>91240</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8020,32 +8022,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R62" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8125,7 +8125,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B63" t="n">
         <v>8447</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R63" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8895,53 +8895,60 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B70" t="n">
-        <v>8361</v>
+        <v>56947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R70" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8970,7 +8977,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8980,7 +8987,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8995,72 +9002,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B71" t="n">
-        <v>56947</v>
+        <v>8361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R71" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9114,12 +9114,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B76" t="n">
-        <v>8436</v>
+        <v>98347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9579,46 +9579,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R76" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9647,7 +9646,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9657,7 +9656,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9672,22 +9671,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B77" t="n">
-        <v>98347</v>
+        <v>8436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9695,45 +9694,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R77" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S77" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9787,12 +9787,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,43 +5954,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>8361</v>
+        <v>98354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5998,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6033,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6043,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,10 +6069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125798802</v>
+        <v>125800234</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98309</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6081,29 +6080,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -6113,13 +6116,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714270</v>
+        <v>714273</v>
       </c>
       <c r="R45" t="n">
-        <v>6395091</v>
+        <v>6395095</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6151,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6161,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,46 +6188,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125800234</v>
+        <v>125797908</v>
       </c>
       <c r="B46" t="n">
-        <v>98302</v>
+        <v>8361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>106540</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714273</v>
+        <v>714352</v>
       </c>
       <c r="R46" t="n">
-        <v>6395095</v>
+        <v>6394957</v>
       </c>
       <c r="S46" t="n">
         <v>18</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6307,7 +6307,7 @@
         <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>125798096</v>
       </c>
       <c r="B48" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>125800049</v>
       </c>
       <c r="B49" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6652,64 +6652,56 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B50" t="n">
-        <v>57932</v>
+        <v>98359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R50" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6738,7 +6730,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6748,7 +6740,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6763,68 +6755,76 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>57932</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R51" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6878,12 +6878,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7009,7 +7009,7 @@
         <v>125797549</v>
       </c>
       <c r="B53" t="n">
-        <v>98302</v>
+        <v>98309</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7332,46 +7332,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125801401</v>
+        <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>98302</v>
+        <v>57648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7379,13 +7375,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714326</v>
+        <v>714316</v>
       </c>
       <c r="R56" t="n">
-        <v>6395124</v>
+        <v>6395075</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7414,7 +7410,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7424,7 +7420,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7451,48 +7447,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799607</v>
+        <v>125801401</v>
       </c>
       <c r="B57" t="n">
-        <v>79476</v>
+        <v>98309</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1026</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714256</v>
+        <v>714326</v>
       </c>
       <c r="R57" t="n">
-        <v>6395083</v>
+        <v>6395124</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7519,9 +7527,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7536,68 +7554,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125799057</v>
+        <v>125799607</v>
       </c>
       <c r="B58" t="n">
-        <v>57648</v>
+        <v>79476</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714316</v>
+        <v>714256</v>
       </c>
       <c r="R58" t="n">
-        <v>6395075</v>
+        <v>6395083</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7624,19 +7634,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7651,12 +7651,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B60" t="n">
-        <v>8361</v>
+        <v>91247</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,32 +7790,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7823,13 +7821,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R60" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7858,7 +7856,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7868,7 +7866,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7895,7 +7893,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B61" t="n">
         <v>8447</v>
@@ -7939,10 +7937,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R61" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7974,7 +7972,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7984,7 +7982,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8011,10 +8009,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B62" t="n">
-        <v>91240</v>
+        <v>8361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8022,30 +8020,32 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R62" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8125,7 +8125,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B63" t="n">
         <v>8447</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R63" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8241,42 +8241,47 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125799922</v>
+        <v>125797646</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>8361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219864</v>
+        <v>106540</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8284,13 +8289,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714240</v>
+        <v>714368</v>
       </c>
       <c r="R64" t="n">
-        <v>6395123</v>
+        <v>6394946</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8334,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8344,59 +8349,54 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125797646</v>
+        <v>125799922</v>
       </c>
       <c r="B65" t="n">
-        <v>8361</v>
+        <v>98359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106540</v>
+        <v>219864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714368</v>
+        <v>714240</v>
       </c>
       <c r="R65" t="n">
-        <v>6394946</v>
+        <v>6395123</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8464,22 +8464,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125800259</v>
+        <v>125797584</v>
       </c>
       <c r="B66" t="n">
-        <v>98347</v>
+        <v>110411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8487,37 +8487,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714261</v>
+        <v>714345</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8544,9 +8548,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8561,22 +8575,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B67" t="n">
-        <v>110404</v>
+        <v>98354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8584,41 +8598,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R67" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S67" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8645,19 +8655,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8672,12 +8672,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8687,7 +8687,7 @@
         <v>125799641</v>
       </c>
       <c r="B68" t="n">
-        <v>95450</v>
+        <v>95457</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>125798280</v>
       </c>
       <c r="B69" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>98302</v>
+        <v>98309</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9337,10 +9337,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800830</v>
+        <v>125798516</v>
       </c>
       <c r="B74" t="n">
-        <v>58128</v>
+        <v>98354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9348,46 +9348,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102625</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714267</v>
+        <v>714263</v>
       </c>
       <c r="R74" t="n">
-        <v>6395077</v>
+        <v>6395090</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9416,7 +9415,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9426,7 +9425,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9441,22 +9440,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125798516</v>
+        <v>125800830</v>
       </c>
       <c r="B75" t="n">
-        <v>98347</v>
+        <v>58128</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9464,45 +9463,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714263</v>
+        <v>714267</v>
       </c>
       <c r="R75" t="n">
-        <v>6395090</v>
+        <v>6395077</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,22 +9556,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B76" t="n">
-        <v>98347</v>
+        <v>8436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9579,45 +9579,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R76" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S76" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9646,7 +9647,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9656,7 +9657,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9671,22 +9672,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B77" t="n">
-        <v>8436</v>
+        <v>98354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9694,46 +9695,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R77" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9787,12 +9787,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>8361</v>
+        <v>85560</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9921,37 +9921,36 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R79" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9980,7 +9979,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9990,7 +9989,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10005,12 +10004,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10020,7 +10019,7 @@
         <v>125797614</v>
       </c>
       <c r="B80" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10124,10 +10123,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125808001</v>
+        <v>125797532</v>
       </c>
       <c r="B81" t="n">
-        <v>85553</v>
+        <v>8361</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10135,36 +10134,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>258917</v>
+        <v>106540</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R81" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,12 +10218,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Max Karlsson, Malte Lindberg, Alec Bailey, Elvira Klang, Filippa Paperin, Elis Lewin, Emilia Blixt, Ivar Anderberg, Nora Toftgård Shahnavaz, Karl Soler Kinnerbäck, Karin Andersson, Erik Christiansson</t>
+          <t>Elias Yngvesson, Max Karlsson, Malte Lindberg, Alec Bailey, Elvira Klang, Filippa Paperin, Elis Lewin, Emilia Blixt, Ivar Anderberg, Nora Toftgård Shahnavaz, Karin Andersson, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6652,56 +6652,64 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B50" t="n">
-        <v>98359</v>
+        <v>57932</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R50" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6730,7 +6738,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6740,7 +6748,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6755,76 +6763,68 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>57932</v>
+        <v>98359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R51" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6878,12 +6878,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -8895,60 +8895,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B70" t="n">
-        <v>56947</v>
+        <v>8361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R70" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8977,7 +8970,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8987,7 +8980,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9002,65 +8995,72 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B71" t="n">
-        <v>8361</v>
+        <v>56947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R71" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9114,12 +9114,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125798516</v>
+        <v>125800830</v>
       </c>
       <c r="B74" t="n">
-        <v>98354</v>
+        <v>58128</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9348,45 +9348,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714263</v>
+        <v>714267</v>
       </c>
       <c r="R74" t="n">
-        <v>6395090</v>
+        <v>6395077</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9415,7 +9416,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9425,7 +9426,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9440,22 +9441,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125800830</v>
+        <v>125798516</v>
       </c>
       <c r="B75" t="n">
-        <v>58128</v>
+        <v>98354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9463,46 +9464,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102625</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714267</v>
+        <v>714263</v>
       </c>
       <c r="R75" t="n">
-        <v>6395077</v>
+        <v>6395090</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,12 +9556,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9799,10 +9799,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808000</v>
+        <v>125797614</v>
       </c>
       <c r="B78" t="n">
-        <v>79476</v>
+        <v>105915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9810,41 +9810,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1026</v>
+        <v>220785</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9873,7 +9869,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9883,7 +9879,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9898,44 +9894,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808001</v>
+        <v>125808000</v>
       </c>
       <c r="B79" t="n">
-        <v>85560</v>
+        <v>79476</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>258917</v>
+        <v>1026</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9979,7 +9980,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10016,48 +10017,47 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125797614</v>
+        <v>125808001</v>
       </c>
       <c r="B80" t="n">
-        <v>105915</v>
+        <v>85560</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R80" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10111,12 +10111,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5957,7 +5957,7 @@
         <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6069,46 +6069,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125800234</v>
+        <v>125797908</v>
       </c>
       <c r="B45" t="n">
-        <v>98309</v>
+        <v>8361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6116,10 +6113,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714273</v>
+        <v>714352</v>
       </c>
       <c r="R45" t="n">
-        <v>6395095</v>
+        <v>6394957</v>
       </c>
       <c r="S45" t="n">
         <v>18</v>
@@ -6151,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6161,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6188,43 +6185,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797908</v>
+        <v>125800234</v>
       </c>
       <c r="B46" t="n">
-        <v>8361</v>
+        <v>98310</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106540</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714352</v>
+        <v>714273</v>
       </c>
       <c r="R46" t="n">
-        <v>6394957</v>
+        <v>6395095</v>
       </c>
       <c r="S46" t="n">
         <v>18</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6304,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>98354</v>
+        <v>91248</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,11 +6339,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6351,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R47" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6386,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6396,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6423,32 +6422,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B48" t="n">
-        <v>91247</v>
+        <v>98355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6458,10 +6457,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6469,13 +6469,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R48" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6544,7 +6544,7 @@
         <v>125800049</v>
       </c>
       <c r="B49" t="n">
-        <v>105267</v>
+        <v>105268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6652,64 +6652,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802957</v>
+        <v>125799723</v>
       </c>
       <c r="B50" t="n">
-        <v>57932</v>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103012</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714254</v>
+        <v>714256</v>
       </c>
       <c r="R50" t="n">
-        <v>6395049</v>
+        <v>6395124</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6738,7 +6731,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6748,7 +6741,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6763,68 +6756,76 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B51" t="n">
-        <v>98359</v>
+        <v>57933</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R51" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6853,7 +6854,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6863,7 +6864,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6878,22 +6879,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125799723</v>
+        <v>125800012</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>98360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6901,32 +6902,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>219864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>714256</v>
+        <v>714239</v>
       </c>
       <c r="R52" t="n">
-        <v>6395124</v>
+        <v>6395154</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7009,7 +7009,7 @@
         <v>125797549</v>
       </c>
       <c r="B53" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>125800687</v>
       </c>
       <c r="B54" t="n">
-        <v>58128</v>
+        <v>58129</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>125799309</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7332,56 +7332,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799057</v>
+        <v>125799607</v>
       </c>
       <c r="B56" t="n">
-        <v>57648</v>
+        <v>79477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714316</v>
+        <v>714256</v>
       </c>
       <c r="R56" t="n">
-        <v>6395075</v>
+        <v>6395083</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7408,19 +7400,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7435,58 +7417,54 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125801401</v>
+        <v>125799057</v>
       </c>
       <c r="B57" t="n">
-        <v>98309</v>
+        <v>57648</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7494,13 +7472,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714326</v>
+        <v>714316</v>
       </c>
       <c r="R57" t="n">
-        <v>6395124</v>
+        <v>6395075</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7529,7 +7507,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7539,7 +7517,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7566,48 +7544,60 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125799607</v>
+        <v>125801401</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>98310</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1026</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714256</v>
+        <v>714326</v>
       </c>
       <c r="R58" t="n">
-        <v>6395083</v>
+        <v>6395124</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7634,9 +7624,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7651,12 +7651,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B60" t="n">
-        <v>91247</v>
+        <v>8361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,30 +7790,32 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7821,13 +7823,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R60" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7856,7 +7858,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7866,7 +7868,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7893,7 +7895,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B61" t="n">
         <v>8447</v>
@@ -7937,10 +7939,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7972,7 +7974,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7982,7 +7984,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8009,10 +8011,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B62" t="n">
-        <v>8361</v>
+        <v>91248</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8020,32 +8022,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R62" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8125,7 +8125,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B63" t="n">
         <v>8447</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R63" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8364,7 +8364,7 @@
         <v>125799922</v>
       </c>
       <c r="B65" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125797584</v>
+        <v>125799641</v>
       </c>
       <c r="B66" t="n">
-        <v>110411</v>
+        <v>95458</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8487,41 +8487,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714345</v>
+        <v>714248</v>
       </c>
       <c r="R66" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S66" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8548,19 +8544,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8575,60 +8561,67 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125800259</v>
+        <v>125798280</v>
       </c>
       <c r="B67" t="n">
-        <v>98354</v>
+        <v>91248</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714261</v>
+        <v>714298</v>
       </c>
       <c r="R67" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8655,9 +8648,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8672,22 +8675,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125799641</v>
+        <v>125800259</v>
       </c>
       <c r="B68" t="n">
-        <v>95457</v>
+        <v>98355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8695,21 +8698,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2779</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8719,7 +8722,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714248</v>
+        <v>714261</v>
       </c>
       <c r="R68" t="n">
         <v>6395081</v>
@@ -8774,48 +8777,45 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125798280</v>
+        <v>125797584</v>
       </c>
       <c r="B69" t="n">
-        <v>91247</v>
+        <v>110412</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8823,13 +8823,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714298</v>
+        <v>714345</v>
       </c>
       <c r="R69" t="n">
-        <v>6395026</v>
+        <v>6394926</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9126,60 +9126,56 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800937</v>
+        <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>57664</v>
+        <v>98355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100048</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R72" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9206,9 +9202,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9223,22 +9229,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800859</v>
+        <v>125800830</v>
       </c>
       <c r="B73" t="n">
-        <v>98309</v>
+        <v>58129</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9246,27 +9252,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9275,13 +9285,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R73" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S73" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9308,9 +9318,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9325,22 +9345,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800830</v>
+        <v>125800859</v>
       </c>
       <c r="B74" t="n">
-        <v>58128</v>
+        <v>98310</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9348,31 +9368,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102625</v>
+        <v>219798</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9381,13 +9397,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R74" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9414,19 +9430,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9441,68 +9447,72 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B75" t="n">
-        <v>98354</v>
+        <v>57664</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R75" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9529,19 +9539,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,22 +9556,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B76" t="n">
-        <v>8436</v>
+        <v>98355</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9579,46 +9579,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R76" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9647,7 +9646,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9657,7 +9656,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9672,22 +9671,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B77" t="n">
-        <v>98354</v>
+        <v>8436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9695,45 +9694,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R77" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S77" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9787,22 +9787,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797614</v>
+        <v>125808000</v>
       </c>
       <c r="B78" t="n">
-        <v>105915</v>
+        <v>79477</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9810,37 +9810,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220785</v>
+        <v>1026</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R78" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9869,7 +9873,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9879,7 +9883,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9894,22 +9898,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808000</v>
+        <v>125797614</v>
       </c>
       <c r="B79" t="n">
-        <v>79476</v>
+        <v>105916</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9917,41 +9921,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1026</v>
+        <v>220785</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R79" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10005,22 +10005,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125808001</v>
+        <v>125797532</v>
       </c>
       <c r="B80" t="n">
-        <v>85560</v>
+        <v>8361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10028,36 +10028,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>258917</v>
+        <v>106540</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R80" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10086,7 +10087,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10096,7 +10097,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10111,22 +10112,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B81" t="n">
-        <v>8361</v>
+        <v>85561</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10134,37 +10135,36 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R81" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10218,12 +10218,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,42 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5997,13 +5998,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,43 +6070,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>8361</v>
+        <v>98357</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R45" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6188,7 +6188,7 @@
         <v>125800234</v>
       </c>
       <c r="B46" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>125801883</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>125800049</v>
       </c>
       <c r="B49" t="n">
-        <v>105268</v>
+        <v>105270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125799723</v>
+        <v>125800012</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>98362</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6663,32 +6663,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6696,13 +6695,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714256</v>
+        <v>714239</v>
       </c>
       <c r="R50" t="n">
-        <v>6395124</v>
+        <v>6395154</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6731,7 +6730,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6741,7 +6740,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6768,64 +6767,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802957</v>
+        <v>125799723</v>
       </c>
       <c r="B51" t="n">
-        <v>57933</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103012</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714254</v>
+        <v>714256</v>
       </c>
       <c r="R51" t="n">
-        <v>6395049</v>
+        <v>6395124</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6854,7 +6846,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6864,7 +6856,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6879,68 +6871,76 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>57933</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R52" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S52" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6994,12 +6994,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7009,7 +7009,7 @@
         <v>125797549</v>
       </c>
       <c r="B53" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>125801401</v>
       </c>
       <c r="B58" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B60" t="n">
-        <v>8361</v>
+        <v>91248</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,32 +7790,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7823,13 +7821,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R60" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7858,7 +7856,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7868,7 +7866,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7895,43 +7893,43 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125798048</v>
+        <v>125798213</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>8361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>106540</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7939,13 +7937,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714313</v>
+        <v>714315</v>
       </c>
       <c r="R61" t="n">
-        <v>6395016</v>
+        <v>6394992</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7974,7 +7972,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7984,7 +7982,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7999,53 +7997,55 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125800799</v>
+        <v>125798048</v>
       </c>
       <c r="B62" t="n">
-        <v>91248</v>
+        <v>8447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714298</v>
+        <v>714313</v>
       </c>
       <c r="R62" t="n">
-        <v>6395044</v>
+        <v>6395016</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8113,12 +8113,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8364,7 +8364,7 @@
         <v>125799922</v>
       </c>
       <c r="B65" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125799641</v>
+        <v>125797584</v>
       </c>
       <c r="B66" t="n">
-        <v>95458</v>
+        <v>110414</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8487,37 +8487,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714248</v>
+        <v>714345</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8544,9 +8548,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8561,67 +8575,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125798280</v>
+        <v>125799641</v>
       </c>
       <c r="B67" t="n">
-        <v>91248</v>
+        <v>95460</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714298</v>
+        <v>714248</v>
       </c>
       <c r="R67" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8648,19 +8655,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8675,60 +8672,67 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125800259</v>
+        <v>125798280</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>91248</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714261</v>
+        <v>714298</v>
       </c>
       <c r="R68" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S68" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8755,9 +8759,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8772,22 +8786,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B69" t="n">
-        <v>110412</v>
+        <v>98357</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8795,41 +8809,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R69" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S69" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8856,19 +8866,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,12 +8883,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9126,56 +9126,60 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B72" t="n">
-        <v>98355</v>
+        <v>57664</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R72" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9202,19 +9206,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9229,12 +9223,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9357,10 +9351,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800859</v>
+        <v>125798516</v>
       </c>
       <c r="B74" t="n">
-        <v>98310</v>
+        <v>98357</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9368,42 +9362,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R74" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S74" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9430,9 +9427,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9447,59 +9454,52 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125800937</v>
+        <v>125800859</v>
       </c>
       <c r="B75" t="n">
-        <v>57664</v>
+        <v>98312</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
@@ -9512,7 +9512,7 @@
         <v>6395124</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9571,7 +9571,7 @@
         <v>125814167</v>
       </c>
       <c r="B76" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9910,32 +9910,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B79" t="n">
-        <v>105916</v>
+        <v>8361</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R79" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10005,44 +10005,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B80" t="n">
-        <v>8361</v>
+        <v>105918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R80" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10112,12 +10112,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -7332,48 +7332,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799607</v>
+        <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>79477</v>
+        <v>57648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1026</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714256</v>
+        <v>714316</v>
       </c>
       <c r="R56" t="n">
-        <v>6395083</v>
+        <v>6395075</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7400,9 +7408,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7417,68 +7435,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799057</v>
+        <v>125799607</v>
       </c>
       <c r="B57" t="n">
-        <v>57648</v>
+        <v>79477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1026</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714316</v>
+        <v>714256</v>
       </c>
       <c r="R57" t="n">
-        <v>6395075</v>
+        <v>6395083</v>
       </c>
       <c r="S57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7505,19 +7515,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7532,12 +7532,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7893,43 +7893,43 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125798213</v>
+        <v>125801701</v>
       </c>
       <c r="B61" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7937,13 +7937,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714315</v>
+        <v>714318</v>
       </c>
       <c r="R61" t="n">
-        <v>6394992</v>
+        <v>6395132</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7997,55 +7997,55 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125798048</v>
+        <v>125798213</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>8361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>106540</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8053,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714313</v>
+        <v>714315</v>
       </c>
       <c r="R62" t="n">
-        <v>6395016</v>
+        <v>6394992</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8113,19 +8113,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B63" t="n">
         <v>8447</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R63" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S63" t="n">
         <v>12</v>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,43 +5954,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>8361</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5998,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6033,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6043,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,10 +6069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125798802</v>
+        <v>125800234</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>98316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6081,29 +6080,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -6113,13 +6116,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714270</v>
+        <v>714273</v>
       </c>
       <c r="R45" t="n">
-        <v>6395091</v>
+        <v>6395095</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6151,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6161,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,46 +6188,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125800234</v>
+        <v>125797908</v>
       </c>
       <c r="B46" t="n">
-        <v>98312</v>
+        <v>8361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>106540</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714273</v>
+        <v>714352</v>
       </c>
       <c r="R46" t="n">
-        <v>6395095</v>
+        <v>6394957</v>
       </c>
       <c r="S46" t="n">
         <v>18</v>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6307,7 +6307,7 @@
         <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>125801883</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>125800049</v>
       </c>
       <c r="B49" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6652,56 +6652,64 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B50" t="n">
-        <v>98362</v>
+        <v>57933</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R50" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6730,7 +6738,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6740,7 +6748,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6755,22 +6763,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799723</v>
+        <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6778,32 +6786,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6811,13 +6818,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714256</v>
+        <v>714239</v>
       </c>
       <c r="R51" t="n">
-        <v>6395124</v>
+        <v>6395154</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6846,7 +6853,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6856,7 +6863,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6883,64 +6890,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802957</v>
+        <v>125799723</v>
       </c>
       <c r="B52" t="n">
-        <v>57933</v>
+        <v>8447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103012</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>714254</v>
+        <v>714256</v>
       </c>
       <c r="R52" t="n">
-        <v>6395049</v>
+        <v>6395124</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6994,12 +6994,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7009,7 +7009,7 @@
         <v>125797549</v>
       </c>
       <c r="B53" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>125799309</v>
       </c>
       <c r="B55" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7447,48 +7447,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799607</v>
+        <v>125801401</v>
       </c>
       <c r="B57" t="n">
-        <v>79477</v>
+        <v>98316</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1026</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714256</v>
+        <v>714326</v>
       </c>
       <c r="R57" t="n">
-        <v>6395083</v>
+        <v>6395124</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7515,9 +7527,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7532,72 +7554,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125801401</v>
+        <v>125799607</v>
       </c>
       <c r="B58" t="n">
-        <v>98312</v>
+        <v>79481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>1026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714326</v>
+        <v>714256</v>
       </c>
       <c r="R58" t="n">
-        <v>6395124</v>
+        <v>6395083</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7624,19 +7634,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7651,12 +7651,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B60" t="n">
-        <v>91248</v>
+        <v>8361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7790,30 +7790,32 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7821,13 +7823,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R60" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7856,7 +7858,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7866,7 +7868,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7893,7 +7895,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B61" t="n">
         <v>8447</v>
@@ -7937,10 +7939,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7972,7 +7974,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7982,7 +7984,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8009,43 +8011,43 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125798213</v>
+        <v>125801701</v>
       </c>
       <c r="B62" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8053,13 +8055,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714315</v>
+        <v>714318</v>
       </c>
       <c r="R62" t="n">
-        <v>6394992</v>
+        <v>6395132</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8088,7 +8090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8098,7 +8100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8113,55 +8115,53 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125798048</v>
+        <v>125800799</v>
       </c>
       <c r="B63" t="n">
-        <v>8447</v>
+        <v>91252</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8169,13 +8169,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714313</v>
+        <v>714298</v>
       </c>
       <c r="R63" t="n">
-        <v>6395016</v>
+        <v>6395044</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8229,12 +8229,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8364,7 +8364,7 @@
         <v>125799922</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B66" t="n">
-        <v>110414</v>
+        <v>98361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8487,41 +8487,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R66" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S66" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8548,19 +8544,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8575,12 +8561,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8590,7 +8576,7 @@
         <v>125799641</v>
       </c>
       <c r="B67" t="n">
-        <v>95460</v>
+        <v>95464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8687,7 +8673,7 @@
         <v>125798280</v>
       </c>
       <c r="B68" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8798,10 +8784,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125800259</v>
+        <v>125797584</v>
       </c>
       <c r="B69" t="n">
-        <v>98357</v>
+        <v>110418</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8809,37 +8795,41 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714261</v>
+        <v>714345</v>
       </c>
       <c r="R69" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8866,9 +8856,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,65 +8883,72 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B70" t="n">
-        <v>8361</v>
+        <v>56947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R70" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8970,7 +8977,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8980,7 +8987,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8995,72 +9002,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B71" t="n">
-        <v>56947</v>
+        <v>8361</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R71" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9114,72 +9114,68 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800937</v>
+        <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>57664</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100048</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R72" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9206,9 +9202,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9223,49 +9229,51 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800830</v>
+        <v>125800937</v>
       </c>
       <c r="B73" t="n">
-        <v>58129</v>
+        <v>57664</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102625</v>
+        <v>100048</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -9273,19 +9281,20 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R73" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9312,19 +9321,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9339,22 +9338,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125798516</v>
+        <v>125800830</v>
       </c>
       <c r="B74" t="n">
-        <v>98357</v>
+        <v>58129</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9362,45 +9361,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714263</v>
+        <v>714267</v>
       </c>
       <c r="R74" t="n">
-        <v>6395090</v>
+        <v>6395077</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9454,12 +9454,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
         <v>125800859</v>
       </c>
       <c r="B75" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B76" t="n">
-        <v>98357</v>
+        <v>8436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9579,45 +9579,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R76" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S76" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9646,7 +9647,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9656,7 +9657,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9671,22 +9672,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B77" t="n">
-        <v>8436</v>
+        <v>98361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9694,46 +9695,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R77" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9787,64 +9787,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808000</v>
+        <v>125797532</v>
       </c>
       <c r="B78" t="n">
-        <v>79477</v>
+        <v>8361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1026</v>
+        <v>106540</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9873,7 +9869,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9883,7 +9879,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9898,22 +9894,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>8361</v>
+        <v>85565</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9921,37 +9917,36 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R79" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9980,7 +9975,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9990,7 +9985,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10005,12 +10000,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10020,7 +10015,7 @@
         <v>125797614</v>
       </c>
       <c r="B80" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10124,32 +10119,37 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125808001</v>
+        <v>125808000</v>
       </c>
       <c r="B81" t="n">
-        <v>85561</v>
+        <v>79481</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>258917</v>
+        <v>1026</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,10 +5954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125800234</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5965,29 +5965,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5997,13 +6001,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714273</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6395095</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6036,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6046,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,46 +6073,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125800234</v>
+        <v>125797908</v>
       </c>
       <c r="B45" t="n">
-        <v>98316</v>
+        <v>8361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6116,10 +6117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714273</v>
+        <v>714352</v>
       </c>
       <c r="R45" t="n">
-        <v>6395095</v>
+        <v>6394957</v>
       </c>
       <c r="S45" t="n">
         <v>18</v>
@@ -6151,7 +6152,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6161,7 +6162,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6188,43 +6189,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B46" t="n">
-        <v>8361</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R46" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S46" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7332,56 +7332,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799057</v>
+        <v>125799607</v>
       </c>
       <c r="B56" t="n">
-        <v>57648</v>
+        <v>79481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714316</v>
+        <v>714256</v>
       </c>
       <c r="R56" t="n">
-        <v>6395075</v>
+        <v>6395083</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7408,19 +7400,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7435,58 +7417,54 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125801401</v>
+        <v>125799057</v>
       </c>
       <c r="B57" t="n">
-        <v>98316</v>
+        <v>57648</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7494,13 +7472,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714326</v>
+        <v>714316</v>
       </c>
       <c r="R57" t="n">
-        <v>6395124</v>
+        <v>6395075</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7529,7 +7507,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7539,7 +7517,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7566,48 +7544,60 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125799607</v>
+        <v>125801401</v>
       </c>
       <c r="B58" t="n">
-        <v>79481</v>
+        <v>98316</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1026</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714256</v>
+        <v>714326</v>
       </c>
       <c r="R58" t="n">
-        <v>6395083</v>
+        <v>6395124</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7634,9 +7624,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7651,12 +7651,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -9799,32 +9799,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B78" t="n">
-        <v>8361</v>
+        <v>105922</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R78" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9894,44 +9894,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808001</v>
+        <v>125808000</v>
       </c>
       <c r="B79" t="n">
-        <v>85565</v>
+        <v>79481</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>258917</v>
+        <v>1026</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9975,7 +9980,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10012,32 +10017,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B80" t="n">
-        <v>105922</v>
+        <v>8361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10047,10 +10052,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R80" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10082,7 +10087,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10092,7 +10097,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10107,49 +10112,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125808000</v>
+        <v>125808001</v>
       </c>
       <c r="B81" t="n">
-        <v>79481</v>
+        <v>85565</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1026</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5954,10 +5954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125800234</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>98316</v>
+        <v>98362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5965,33 +5965,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -6001,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714273</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6395095</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6036,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6046,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6189,42 +6185,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125798802</v>
+        <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>91252</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714270</v>
+        <v>714304</v>
       </c>
       <c r="R46" t="n">
-        <v>6395091</v>
+        <v>6395005</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6276,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6303,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>91252</v>
+        <v>98362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,10 +6338,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R47" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125801883</v>
+        <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>105275</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6433,33 +6433,25 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>221141</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -6469,13 +6461,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>714372</v>
+        <v>714240</v>
       </c>
       <c r="R48" t="n">
-        <v>6395100</v>
+        <v>6395175</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6504,7 +6496,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6514,7 +6506,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6541,10 +6533,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125800049</v>
+        <v>125799723</v>
       </c>
       <c r="B49" t="n">
-        <v>105274</v>
+        <v>8447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6552,27 +6544,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221141</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6580,13 +6577,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714240</v>
+        <v>714256</v>
       </c>
       <c r="R49" t="n">
-        <v>6395175</v>
+        <v>6395124</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6615,7 +6612,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6625,7 +6622,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6778,7 +6775,7 @@
         <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6890,10 +6887,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125799723</v>
+        <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>98317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6901,32 +6898,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6934,10 +6930,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>714256</v>
+        <v>714361</v>
       </c>
       <c r="R52" t="n">
-        <v>6395124</v>
+        <v>6394936</v>
       </c>
       <c r="S52" t="n">
         <v>11</v>
@@ -6969,7 +6965,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6979,7 +6975,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7006,10 +7002,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125797549</v>
+        <v>125800687</v>
       </c>
       <c r="B53" t="n">
-        <v>98316</v>
+        <v>58129</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7017,45 +7013,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>714361</v>
+        <v>714279</v>
       </c>
       <c r="R53" t="n">
-        <v>6394936</v>
+        <v>6395109</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7082,19 +7074,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7109,64 +7091,63 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Camilla Edvinsson, Nora Toftgård Shahnavaz, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125800687</v>
+        <v>125799309</v>
       </c>
       <c r="B54" t="n">
-        <v>58129</v>
+        <v>79481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102625</v>
+        <v>1026</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>714279</v>
+        <v>714260</v>
       </c>
       <c r="R54" t="n">
-        <v>6395109</v>
+        <v>6395087</v>
       </c>
       <c r="S54" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7193,9 +7174,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7210,49 +7201,54 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Camilla Edvinsson, Nora Toftgård Shahnavaz, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125799309</v>
+        <v>125799057</v>
       </c>
       <c r="B55" t="n">
-        <v>79481</v>
+        <v>57648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1026</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7260,13 +7256,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>714260</v>
+        <v>714316</v>
       </c>
       <c r="R55" t="n">
-        <v>6395087</v>
+        <v>6395075</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7295,7 +7291,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7305,7 +7301,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7320,12 +7316,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7429,10 +7425,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799057</v>
+        <v>125798798</v>
       </c>
       <c r="B57" t="n">
-        <v>57648</v>
+        <v>8361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7440,29 +7436,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>106540</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7472,13 +7469,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>714316</v>
+        <v>714270</v>
       </c>
       <c r="R57" t="n">
-        <v>6395075</v>
+        <v>6395091</v>
       </c>
       <c r="S57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7507,7 +7504,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7517,7 +7514,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7544,46 +7541,41 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125801401</v>
+        <v>125800799</v>
       </c>
       <c r="B58" t="n">
-        <v>98316</v>
+        <v>91252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7591,13 +7583,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714326</v>
+        <v>714298</v>
       </c>
       <c r="R58" t="n">
-        <v>6395124</v>
+        <v>6395044</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7626,7 +7618,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7636,7 +7628,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7651,19 +7643,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798798</v>
+        <v>125798213</v>
       </c>
       <c r="B59" t="n">
         <v>8361</v>
@@ -7691,15 +7683,15 @@
           <t>(Fabricius, 1787)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7707,13 +7699,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714270</v>
+        <v>714315</v>
       </c>
       <c r="R59" t="n">
-        <v>6395091</v>
+        <v>6394992</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7742,7 +7734,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7752,7 +7744,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7767,55 +7759,55 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798213</v>
+        <v>125798048</v>
       </c>
       <c r="B60" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7823,13 +7815,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714315</v>
+        <v>714313</v>
       </c>
       <c r="R60" t="n">
-        <v>6394992</v>
+        <v>6395016</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7858,7 +7850,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7868,7 +7860,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7883,19 +7875,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B61" t="n">
         <v>8447</v>
@@ -7939,10 +7931,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R61" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -7974,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7984,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8011,10 +8003,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125801701</v>
+        <v>125799922</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>98367</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8022,32 +8014,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8055,13 +8046,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714318</v>
+        <v>714240</v>
       </c>
       <c r="R62" t="n">
-        <v>6395132</v>
+        <v>6395123</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8090,7 +8081,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8100,7 +8091,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8127,10 +8118,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125800799</v>
+        <v>125797646</v>
       </c>
       <c r="B63" t="n">
-        <v>91252</v>
+        <v>8361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,30 +8129,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8169,13 +8166,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714298</v>
+        <v>714368</v>
       </c>
       <c r="R63" t="n">
-        <v>6395044</v>
+        <v>6394946</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8204,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8214,7 +8211,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8241,61 +8238,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125797646</v>
+        <v>125799641</v>
       </c>
       <c r="B64" t="n">
-        <v>8361</v>
+        <v>95465</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106540</v>
+        <v>2779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714368</v>
+        <v>714248</v>
       </c>
       <c r="R64" t="n">
-        <v>6394946</v>
+        <v>6395081</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8322,19 +8306,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8349,54 +8323,53 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125799922</v>
+        <v>125798280</v>
       </c>
       <c r="B65" t="n">
-        <v>98366</v>
+        <v>91252</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219864</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8404,13 +8377,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714240</v>
+        <v>714298</v>
       </c>
       <c r="R65" t="n">
-        <v>6395123</v>
+        <v>6395026</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8439,7 +8412,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8449,7 +8422,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8476,10 +8449,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125800259</v>
+        <v>125797584</v>
       </c>
       <c r="B66" t="n">
-        <v>98361</v>
+        <v>110419</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8487,37 +8460,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714261</v>
+        <v>714345</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8544,9 +8521,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8561,22 +8548,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125799641</v>
+        <v>125800259</v>
       </c>
       <c r="B67" t="n">
-        <v>95464</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8584,21 +8571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2779</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8608,7 +8595,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714248</v>
+        <v>714261</v>
       </c>
       <c r="R67" t="n">
         <v>6395081</v>
@@ -8663,17 +8650,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125798280</v>
+        <v>125798187</v>
       </c>
       <c r="B68" t="n">
-        <v>91252</v>
+        <v>8361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8681,30 +8668,28 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8712,13 +8697,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714298</v>
+        <v>714301</v>
       </c>
       <c r="R68" t="n">
-        <v>6395026</v>
+        <v>6395029</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8747,7 +8732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8757,7 +8742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8784,10 +8769,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125797584</v>
+        <v>125814124</v>
       </c>
       <c r="B69" t="n">
-        <v>110418</v>
+        <v>56947</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8795,41 +8780,49 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219711</v>
+        <v>100038</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714345</v>
+        <v>714386</v>
       </c>
       <c r="R69" t="n">
-        <v>6394926</v>
+        <v>6395050</v>
       </c>
       <c r="S69" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8858,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8868,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8883,22 +8876,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125814124</v>
+        <v>125798516</v>
       </c>
       <c r="B70" t="n">
-        <v>56947</v>
+        <v>98362</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8906,49 +8899,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100038</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714386</v>
+        <v>714263</v>
       </c>
       <c r="R70" t="n">
-        <v>6395050</v>
+        <v>6395090</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8977,7 +8966,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8987,7 +8976,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9002,22 +8991,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125798187</v>
+        <v>125800937</v>
       </c>
       <c r="B71" t="n">
-        <v>8361</v>
+        <v>57664</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9025,42 +9014,49 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106540</v>
+        <v>100048</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714301</v>
+        <v>714265</v>
       </c>
       <c r="R71" t="n">
-        <v>6395029</v>
+        <v>6395124</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9087,19 +9083,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9114,22 +9100,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125798516</v>
+        <v>125800830</v>
       </c>
       <c r="B72" t="n">
-        <v>98361</v>
+        <v>58129</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9137,45 +9123,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714263</v>
+        <v>714267</v>
       </c>
       <c r="R72" t="n">
-        <v>6395090</v>
+        <v>6395077</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9204,7 +9191,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9214,7 +9201,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9229,59 +9216,52 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800937</v>
+        <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>57664</v>
+        <v>98317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
@@ -9294,7 +9274,7 @@
         <v>6395124</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9343,17 +9323,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800830</v>
+        <v>125800866</v>
       </c>
       <c r="B74" t="n">
-        <v>58129</v>
+        <v>8436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9361,46 +9341,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102625</v>
+        <v>106554</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714267</v>
+        <v>714279</v>
       </c>
       <c r="R74" t="n">
-        <v>6395077</v>
+        <v>6395120</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9429,7 +9409,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9439,7 +9419,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9454,22 +9434,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125800859</v>
+        <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98316</v>
+        <v>98362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9477,42 +9457,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714265</v>
+        <v>714271</v>
       </c>
       <c r="R75" t="n">
-        <v>6395124</v>
+        <v>6395065</v>
       </c>
       <c r="S75" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9539,9 +9522,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9556,69 +9549,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125800866</v>
+        <v>125797614</v>
       </c>
       <c r="B76" t="n">
-        <v>8436</v>
+        <v>105923</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>220785</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714279</v>
+        <v>714333</v>
       </c>
       <c r="R76" t="n">
-        <v>6395120</v>
+        <v>6394948</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9647,7 +9631,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9657,7 +9641,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9672,68 +9656,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125814167</v>
+        <v>125797532</v>
       </c>
       <c r="B77" t="n">
-        <v>98361</v>
+        <v>8361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714271</v>
+        <v>714342</v>
       </c>
       <c r="R77" t="n">
-        <v>6395065</v>
+        <v>6394935</v>
       </c>
       <c r="S77" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9762,7 +9738,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9772,7 +9748,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9787,22 +9763,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797614</v>
+        <v>125808000</v>
       </c>
       <c r="B78" t="n">
-        <v>105922</v>
+        <v>79481</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9810,37 +9786,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220785</v>
+        <v>1026</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R78" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9869,7 +9849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9879,7 +9859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9894,49 +9874,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808000</v>
+        <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>79481</v>
+        <v>85565</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1026</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9980,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10017,10 +9992,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125797532</v>
+        <v>125800805</v>
       </c>
       <c r="B80" t="n">
-        <v>8361</v>
+        <v>5166</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10028,37 +10003,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106540</v>
+        <v>100276</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Prydnadsbock</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Anaglyptus mysticus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Fole lund, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>714342</v>
+        <v>714269</v>
       </c>
       <c r="R80" t="n">
-        <v>6394935</v>
+        <v>6395114</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10085,86 +10069,110 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Corylus avellana</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Elias Yngvesson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Elias Yngvesson, Max Karlsson, Malte Lindberg, Alec Bailey, Elvira Klang, Filippa Paperin, Elis Lewin, Emilia Blixt, Ivar Anderberg, Nora Toftgård Shahnavaz, Karin Andersson, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125808001</v>
+        <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>85565</v>
+        <v>98317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>258917</v>
+        <v>219798</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>714264</v>
+        <v>714273</v>
       </c>
       <c r="R81" t="n">
-        <v>6395004</v>
+        <v>6395095</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10193,7 +10201,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10203,7 +10211,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10212,75 +10220,71 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125800805</v>
+        <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>5166</v>
+        <v>100521</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100276</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Prydnadsbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anaglyptus mysticus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fole lund, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>714269</v>
+        <v>714240</v>
       </c>
       <c r="R82" t="n">
-        <v>6395114</v>
+        <v>6395123</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10322,38 +10326,254 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Corylus avellana</t>
-        </is>
-      </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Max Karlsson, Malte Lindberg, Alec Bailey, Elvira Klang, Filippa Paperin, Elis Lewin, Emilia Blixt, Ivar Anderberg, Nora Toftgård Shahnavaz, Karin Andersson, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125801401</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Änge gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>714326</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6395124</v>
+      </c>
+      <c r="S83" t="n">
+        <v>12</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125797737</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Änge Gamla tomt, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>714375</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6394988</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,42 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98362</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5997,13 +5998,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,43 +6070,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>8361</v>
+        <v>98362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R45" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7213,56 +7213,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125799057</v>
+        <v>125799607</v>
       </c>
       <c r="B55" t="n">
-        <v>57648</v>
+        <v>79481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>714316</v>
+        <v>714256</v>
       </c>
       <c r="R55" t="n">
-        <v>6395075</v>
+        <v>6395083</v>
       </c>
       <c r="S55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7289,19 +7281,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7316,60 +7298,68 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799607</v>
+        <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>79481</v>
+        <v>57648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1026</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>714256</v>
+        <v>714316</v>
       </c>
       <c r="R56" t="n">
-        <v>6395083</v>
+        <v>6395075</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7396,9 +7386,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7413,12 +7413,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B58" t="n">
-        <v>91252</v>
+        <v>8361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7552,30 +7552,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7583,13 +7585,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R58" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7618,7 +7620,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7628,7 +7630,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7655,43 +7657,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798213</v>
+        <v>125798048</v>
       </c>
       <c r="B59" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7699,13 +7701,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714315</v>
+        <v>714313</v>
       </c>
       <c r="R59" t="n">
-        <v>6394992</v>
+        <v>6395016</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7734,7 +7736,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7744,7 +7746,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7759,19 +7761,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B60" t="n">
         <v>8447</v>
@@ -7815,10 +7817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R60" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -7850,7 +7852,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7860,7 +7862,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7887,43 +7889,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125800799</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>91252</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714298</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395044</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7991,12 +7991,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125799641</v>
+        <v>125797584</v>
       </c>
       <c r="B64" t="n">
-        <v>95465</v>
+        <v>110419</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,37 +8249,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2779</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714248</v>
+        <v>714345</v>
       </c>
       <c r="R64" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8306,9 +8310,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8323,67 +8337,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125798280</v>
+        <v>125800259</v>
       </c>
       <c r="B65" t="n">
-        <v>91252</v>
+        <v>98362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714298</v>
+        <v>714261</v>
       </c>
       <c r="R65" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8410,19 +8417,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8437,50 +8434,53 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125797584</v>
+        <v>125798280</v>
       </c>
       <c r="B66" t="n">
-        <v>110419</v>
+        <v>91252</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714345</v>
+        <v>714298</v>
       </c>
       <c r="R66" t="n">
-        <v>6394926</v>
+        <v>6395026</v>
       </c>
       <c r="S66" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8560,10 +8560,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125800259</v>
+        <v>125799641</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>95465</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8571,21 +8571,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>2779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714261</v>
+        <v>714248</v>
       </c>
       <c r="R67" t="n">
         <v>6395081</v>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,43 +5954,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>8361</v>
+        <v>98362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5998,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6033,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6043,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,42 +6069,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B45" t="n">
-        <v>98362</v>
+        <v>8361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R45" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B46" t="n">
-        <v>91252</v>
+        <v>98362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,10 +6220,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6231,13 +6232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R46" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6266,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6276,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,32 +6304,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>98362</v>
+        <v>91252</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6338,11 +6339,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R47" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6533,57 +6533,64 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125799723</v>
+        <v>125802957</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>57933</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>103012</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714256</v>
+        <v>714254</v>
       </c>
       <c r="R49" t="n">
-        <v>6395124</v>
+        <v>6395049</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6612,7 +6619,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6622,7 +6629,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6637,76 +6644,68 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B50" t="n">
-        <v>57933</v>
+        <v>98367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R50" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6735,7 +6734,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6745,7 +6744,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6760,22 +6759,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800012</v>
+        <v>125799723</v>
       </c>
       <c r="B51" t="n">
-        <v>98367</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6783,31 +6782,32 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714239</v>
+        <v>714256</v>
       </c>
       <c r="R51" t="n">
-        <v>6395154</v>
+        <v>6395124</v>
       </c>
       <c r="S51" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -8003,42 +8003,47 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125799922</v>
+        <v>125797646</v>
       </c>
       <c r="B62" t="n">
-        <v>98367</v>
+        <v>8361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>106540</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8046,13 +8051,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714240</v>
+        <v>714368</v>
       </c>
       <c r="R62" t="n">
-        <v>6395123</v>
+        <v>6394946</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8081,7 +8086,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8091,7 +8096,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8106,59 +8111,54 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125797646</v>
+        <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>8361</v>
+        <v>98367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106540</v>
+        <v>219864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714368</v>
+        <v>714240</v>
       </c>
       <c r="R63" t="n">
-        <v>6394946</v>
+        <v>6395123</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8226,12 +8226,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,42 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98362</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5997,13 +5998,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,43 +6070,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>8361</v>
+        <v>98364</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R45" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>98362</v>
+        <v>91254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,11 +6220,10 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R46" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6276,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6303,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>91252</v>
+        <v>98364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,10 +6338,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R47" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6533,64 +6533,56 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B49" t="n">
-        <v>57933</v>
+        <v>98369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R49" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6619,7 +6611,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6629,7 +6621,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6644,22 +6636,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125800012</v>
+        <v>125799723</v>
       </c>
       <c r="B50" t="n">
-        <v>98367</v>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6667,31 +6659,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6699,13 +6692,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714239</v>
+        <v>714256</v>
       </c>
       <c r="R50" t="n">
-        <v>6395154</v>
+        <v>6395124</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6734,7 +6727,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6744,7 +6737,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6771,57 +6764,64 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799723</v>
+        <v>125802957</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>57934</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>103012</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714256</v>
+        <v>714254</v>
       </c>
       <c r="R51" t="n">
-        <v>6395124</v>
+        <v>6395049</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,12 +6875,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>125800687</v>
       </c>
       <c r="B53" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>125799309</v>
       </c>
       <c r="B54" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>125799607</v>
       </c>
       <c r="B55" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B58" t="n">
-        <v>8361</v>
+        <v>91254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7552,32 +7552,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7585,13 +7583,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R58" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7620,7 +7618,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7630,7 +7628,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7657,7 +7655,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B59" t="n">
         <v>8447</v>
@@ -7701,10 +7699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R59" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -7736,7 +7734,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7746,7 +7744,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7773,7 +7771,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B60" t="n">
         <v>8447</v>
@@ -7817,10 +7815,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R60" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -7852,7 +7850,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7862,7 +7860,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7889,10 +7887,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B61" t="n">
-        <v>91252</v>
+        <v>8361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7900,30 +7898,32 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R61" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8126,7 +8126,7 @@
         <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B64" t="n">
-        <v>110419</v>
+        <v>98364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,41 +8249,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R64" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8310,19 +8306,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8337,22 +8323,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125800259</v>
+        <v>125797584</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>110421</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8360,37 +8346,41 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714261</v>
+        <v>714345</v>
       </c>
       <c r="R65" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S65" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8417,9 +8407,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8434,67 +8434,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125798280</v>
+        <v>125799641</v>
       </c>
       <c r="B66" t="n">
-        <v>91252</v>
+        <v>95467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714298</v>
+        <v>714248</v>
       </c>
       <c r="R66" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8521,19 +8514,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8548,60 +8531,67 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125799641</v>
+        <v>125798280</v>
       </c>
       <c r="B67" t="n">
-        <v>95465</v>
+        <v>91254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714248</v>
+        <v>714298</v>
       </c>
       <c r="R67" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8628,9 +8618,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8645,65 +8645,72 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B68" t="n">
-        <v>8361</v>
+        <v>56948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R68" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8732,7 +8739,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8742,7 +8749,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8757,72 +8764,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B69" t="n">
-        <v>56947</v>
+        <v>8361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R69" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,68 +8876,72 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B70" t="n">
-        <v>98362</v>
+        <v>57665</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R70" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8964,19 +8968,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8991,51 +8985,49 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800937</v>
+        <v>125800830</v>
       </c>
       <c r="B71" t="n">
-        <v>57664</v>
+        <v>58130</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100048</v>
+        <v>102625</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9043,20 +9035,19 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R71" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9083,9 +9074,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9100,22 +9101,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800830</v>
+        <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>58129</v>
+        <v>98364</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9123,46 +9124,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102625</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714267</v>
+        <v>714263</v>
       </c>
       <c r="R72" t="n">
-        <v>6395077</v>
+        <v>6395090</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9216,12 +9216,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9231,7 +9231,7 @@
         <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B74" t="n">
-        <v>8436</v>
+        <v>98364</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9341,46 +9341,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R74" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9409,7 +9408,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9419,7 +9418,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9434,22 +9433,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B75" t="n">
-        <v>98362</v>
+        <v>8436</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9457,45 +9456,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R75" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S75" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,44 +9549,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B76" t="n">
-        <v>105923</v>
+        <v>8361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R76" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9656,44 +9656,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B77" t="n">
-        <v>8361</v>
+        <v>105925</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R77" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9763,12 +9763,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9778,7 +9778,7 @@
         <v>125808000</v>
       </c>
       <c r="B78" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>85565</v>
+        <v>85566</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -8335,10 +8335,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125797584</v>
+        <v>125799641</v>
       </c>
       <c r="B65" t="n">
-        <v>110421</v>
+        <v>95467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8346,41 +8346,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714345</v>
+        <v>714248</v>
       </c>
       <c r="R65" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S65" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8407,19 +8403,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8434,60 +8420,67 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125799641</v>
+        <v>125798280</v>
       </c>
       <c r="B66" t="n">
-        <v>95467</v>
+        <v>91254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714248</v>
+        <v>714298</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8514,9 +8507,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8531,53 +8534,50 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125798280</v>
+        <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>91254</v>
+        <v>110421</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714298</v>
+        <v>714345</v>
       </c>
       <c r="R67" t="n">
-        <v>6395026</v>
+        <v>6394926</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9330,10 +9330,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B74" t="n">
-        <v>98364</v>
+        <v>8436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9341,45 +9341,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R74" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S74" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9408,7 +9409,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9418,7 +9419,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9433,22 +9434,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>8436</v>
+        <v>98364</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9456,46 +9457,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R75" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,12 +9549,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,43 +5954,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>8361</v>
+        <v>98366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5998,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6033,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6043,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,42 +6069,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B45" t="n">
-        <v>98364</v>
+        <v>8361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R45" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B46" t="n">
-        <v>91254</v>
+        <v>98366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,10 +6220,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6231,13 +6232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R46" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6266,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6276,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,32 +6304,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>98364</v>
+        <v>91256</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6338,11 +6339,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R47" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105277</v>
+        <v>105279</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125800012</v>
+        <v>125799723</v>
       </c>
       <c r="B49" t="n">
-        <v>98369</v>
+        <v>8447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6544,31 +6544,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219864</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6576,13 +6577,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714239</v>
+        <v>714256</v>
       </c>
       <c r="R49" t="n">
-        <v>6395154</v>
+        <v>6395124</v>
       </c>
       <c r="S49" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6611,7 +6612,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6621,7 +6622,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6648,57 +6649,64 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125799723</v>
+        <v>125802957</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>57934</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>103012</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714256</v>
+        <v>714254</v>
       </c>
       <c r="R50" t="n">
-        <v>6395124</v>
+        <v>6395049</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6727,7 +6735,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6737,7 +6745,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6752,76 +6760,68 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Max Karlsson, Malte Lindberg, Karl Soler Kinnerbäck, Karin Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elis Lewin, Elias Yngvesson, Alec Bailey, Elvira Klang</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>57934</v>
+        <v>98371</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R51" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,12 +6875,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Camilla Edvinsson, Nora Toftgård Shahnavaz, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
+          <t>Nora Toftgård Shahnavaz, Camilla Edvinsson, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B58" t="n">
-        <v>91254</v>
+        <v>8361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7552,30 +7552,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7583,13 +7585,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R58" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7618,7 +7620,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7628,7 +7630,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7655,7 +7657,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B59" t="n">
         <v>8447</v>
@@ -7699,10 +7701,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R59" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -7734,7 +7736,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7744,7 +7746,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7771,7 +7773,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798048</v>
+        <v>125801701</v>
       </c>
       <c r="B60" t="n">
         <v>8447</v>
@@ -7815,10 +7817,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714313</v>
+        <v>714318</v>
       </c>
       <c r="R60" t="n">
-        <v>6395016</v>
+        <v>6395132</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -7850,7 +7852,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7860,7 +7862,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7887,10 +7889,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B61" t="n">
-        <v>8361</v>
+        <v>91256</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7898,32 +7900,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R61" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8126,7 +8126,7 @@
         <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>125800259</v>
       </c>
       <c r="B64" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>125799641</v>
       </c>
       <c r="B65" t="n">
-        <v>95467</v>
+        <v>95469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>125798280</v>
       </c>
       <c r="B66" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9116,7 +9116,7 @@
         <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9554,39 +9554,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B76" t="n">
-        <v>8361</v>
+        <v>105927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R76" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9656,44 +9656,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B77" t="n">
-        <v>105925</v>
+        <v>8361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R77" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9763,12 +9763,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9889,7 +9889,7 @@
         <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>85566</v>
+        <v>85568</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,42 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98366</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5997,13 +5998,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,43 +6070,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>8361</v>
+        <v>98366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R45" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7773,43 +7773,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125801701</v>
+        <v>125800799</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>91256</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7817,13 +7815,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714318</v>
+        <v>714298</v>
       </c>
       <c r="R60" t="n">
-        <v>6395132</v>
+        <v>6395044</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7852,7 +7850,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7862,7 +7860,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7877,53 +7875,55 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125800799</v>
+        <v>125801701</v>
       </c>
       <c r="B61" t="n">
-        <v>91256</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714298</v>
+        <v>714318</v>
       </c>
       <c r="R61" t="n">
-        <v>6395044</v>
+        <v>6395132</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7991,12 +7991,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8888,47 +8888,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125800937</v>
+        <v>125800859</v>
       </c>
       <c r="B70" t="n">
-        <v>57665</v>
+        <v>98321</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
@@ -8941,7 +8934,7 @@
         <v>6395124</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8990,17 +8983,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800830</v>
+        <v>125798516</v>
       </c>
       <c r="B71" t="n">
-        <v>58130</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9008,46 +9001,45 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102625</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714267</v>
+        <v>714263</v>
       </c>
       <c r="R71" t="n">
-        <v>6395077</v>
+        <v>6395090</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9076,7 +9068,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9086,7 +9078,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9101,68 +9093,72 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B72" t="n">
-        <v>98366</v>
+        <v>57665</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R72" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9189,19 +9185,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9216,22 +9202,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800859</v>
+        <v>125800830</v>
       </c>
       <c r="B73" t="n">
-        <v>98321</v>
+        <v>58130</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9239,27 +9225,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9268,13 +9258,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R73" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S73" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9301,9 +9291,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9318,12 +9318,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9561,10 +9561,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125797614</v>
+        <v>125808000</v>
       </c>
       <c r="B76" t="n">
-        <v>105927</v>
+        <v>79482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9572,37 +9572,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220785</v>
+        <v>1026</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R76" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9631,7 +9635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9641,7 +9645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9656,22 +9660,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B77" t="n">
-        <v>8361</v>
+        <v>85568</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9679,37 +9683,36 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R77" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9738,7 +9741,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9748,7 +9751,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9763,64 +9766,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808000</v>
+        <v>125797532</v>
       </c>
       <c r="B78" t="n">
-        <v>79482</v>
+        <v>8361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1026</v>
+        <v>106540</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9849,7 +9848,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9859,7 +9858,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9874,59 +9873,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808001</v>
+        <v>125797614</v>
       </c>
       <c r="B79" t="n">
-        <v>85568</v>
+        <v>105927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>258917</v>
+        <v>220785</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R79" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9980,12 +9980,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,43 +5954,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B44" t="n">
-        <v>8361</v>
+        <v>98368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5998,13 +5997,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R44" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6033,7 +6032,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6043,7 +6042,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,42 +6069,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B45" t="n">
-        <v>98366</v>
+        <v>8361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R45" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>98366</v>
+        <v>91258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,11 +6220,10 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R46" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6276,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6303,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>91256</v>
+        <v>98368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,10 +6338,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R47" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105279</v>
+        <v>105283</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Camilla Edvinsson, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
+          <t>Camilla Edvinsson, Nora Toftgård Shahnavaz, Filippa Paperin, Elvira Klang, Alec Bailey, Johanna Vanberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7773,41 +7773,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125800799</v>
+        <v>125801701</v>
       </c>
       <c r="B60" t="n">
-        <v>91256</v>
+        <v>8447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7815,13 +7817,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714298</v>
+        <v>714318</v>
       </c>
       <c r="R60" t="n">
-        <v>6395044</v>
+        <v>6395132</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7850,7 +7852,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7860,7 +7862,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7875,55 +7877,53 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125800799</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>91258</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714298</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395044</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7991,12 +7991,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
         <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>98371</v>
+        <v>98373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8238,48 +8238,55 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125800259</v>
+        <v>125798280</v>
       </c>
       <c r="B64" t="n">
-        <v>98366</v>
+        <v>91258</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714261</v>
+        <v>714298</v>
       </c>
       <c r="R64" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S64" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8306,9 +8313,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8323,22 +8340,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125799641</v>
+        <v>125800259</v>
       </c>
       <c r="B65" t="n">
-        <v>95469</v>
+        <v>98368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8346,21 +8363,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2779</v>
+        <v>219847</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8370,7 +8387,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714248</v>
+        <v>714261</v>
       </c>
       <c r="R65" t="n">
         <v>6395081</v>
@@ -8425,62 +8442,55 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125798280</v>
+        <v>125799641</v>
       </c>
       <c r="B66" t="n">
-        <v>91256</v>
+        <v>95471</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714298</v>
+        <v>714248</v>
       </c>
       <c r="R66" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8507,19 +8517,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8534,12 +8534,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8549,7 +8549,7 @@
         <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8888,10 +8888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125800859</v>
+        <v>125800830</v>
       </c>
       <c r="B70" t="n">
-        <v>98321</v>
+        <v>58130</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8899,27 +8899,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8928,13 +8932,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R70" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S70" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8961,9 +8965,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8978,68 +8992,72 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>57665</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R71" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9066,19 +9084,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9093,72 +9101,68 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Johanna Vanberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800937</v>
+        <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>57665</v>
+        <v>98368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100048</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R72" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9185,9 +9189,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9202,22 +9216,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800830</v>
+        <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>58130</v>
+        <v>98323</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9225,31 +9239,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102625</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9258,13 +9268,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R73" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9291,19 +9301,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9318,12 +9318,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9449,7 +9449,7 @@
         <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9672,47 +9672,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125808001</v>
+        <v>125797614</v>
       </c>
       <c r="B77" t="n">
-        <v>85568</v>
+        <v>105931</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>258917</v>
+        <v>220785</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R77" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9741,7 +9742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9751,7 +9752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9766,22 +9767,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B78" t="n">
-        <v>8361</v>
+        <v>85569</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9789,37 +9790,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R78" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9873,44 +9873,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B79" t="n">
-        <v>105927</v>
+        <v>8361</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R79" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9980,12 +9980,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B46" t="n">
-        <v>91258</v>
+        <v>98368</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,10 +6220,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6231,13 +6232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R46" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6266,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6276,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,32 +6304,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>98368</v>
+        <v>91258</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6338,11 +6339,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R47" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -8888,10 +8888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125800830</v>
+        <v>125798516</v>
       </c>
       <c r="B70" t="n">
-        <v>58130</v>
+        <v>98368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8899,46 +8899,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102625</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714267</v>
+        <v>714263</v>
       </c>
       <c r="R70" t="n">
-        <v>6395077</v>
+        <v>6395090</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8967,7 +8966,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8977,7 +8976,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8992,59 +8991,52 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800937</v>
+        <v>125800859</v>
       </c>
       <c r="B71" t="n">
-        <v>57665</v>
+        <v>98323</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
@@ -9057,7 +9049,7 @@
         <v>6395124</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9106,63 +9098,67 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Johanna Vanberg, Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B72" t="n">
-        <v>98368</v>
+        <v>57665</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R72" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9189,19 +9185,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9216,22 +9202,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Johanna Vanberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800859</v>
+        <v>125800830</v>
       </c>
       <c r="B73" t="n">
-        <v>98323</v>
+        <v>58130</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9239,27 +9225,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9268,13 +9258,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R73" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S73" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9301,9 +9291,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9318,12 +9318,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -5954,42 +5954,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125798802</v>
+        <v>125797908</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>8361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>106540</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5997,13 +5998,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>714270</v>
+        <v>714352</v>
       </c>
       <c r="R44" t="n">
-        <v>6395091</v>
+        <v>6394957</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6032,7 +6033,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6042,7 +6043,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6069,43 +6070,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797908</v>
+        <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>8361</v>
+        <v>98372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6113,13 +6113,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>714352</v>
+        <v>714270</v>
       </c>
       <c r="R45" t="n">
-        <v>6394957</v>
+        <v>6395091</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>91262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,11 +6220,10 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R46" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6276,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6303,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>91258</v>
+        <v>98372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,10 +6338,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R47" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105283</v>
+        <v>105296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>125802957</v>
       </c>
       <c r="B50" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Max Karlsson, Malte Lindberg, Karl Soler Kinnerbäck, Karin Andersson, Ivar Anderberg, Filippa Paperin, Erik Christiansson, Emilia Blixt, Elis Lewin, Elias Yngvesson, Alec Bailey, Elvira Klang</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6775,7 +6775,7 @@
         <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>125800687</v>
       </c>
       <c r="B53" t="n">
-        <v>58130</v>
+        <v>58134</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>125799309</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>125799607</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125798213</v>
+        <v>125800799</v>
       </c>
       <c r="B58" t="n">
-        <v>8361</v>
+        <v>91262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7552,32 +7552,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106540</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7585,13 +7583,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714315</v>
+        <v>714298</v>
       </c>
       <c r="R58" t="n">
-        <v>6394992</v>
+        <v>6395044</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7620,7 +7618,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7630,7 +7628,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7657,43 +7655,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798048</v>
+        <v>125798213</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>8361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>106540</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7701,13 +7699,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714313</v>
+        <v>714315</v>
       </c>
       <c r="R59" t="n">
-        <v>6395016</v>
+        <v>6394992</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7736,7 +7734,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7746,7 +7744,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7761,19 +7759,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125801701</v>
+        <v>125798048</v>
       </c>
       <c r="B60" t="n">
         <v>8447</v>
@@ -7817,10 +7815,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714318</v>
+        <v>714313</v>
       </c>
       <c r="R60" t="n">
-        <v>6395132</v>
+        <v>6395016</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -7852,7 +7850,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7862,7 +7860,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7889,41 +7887,43 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125800799</v>
+        <v>125801701</v>
       </c>
       <c r="B61" t="n">
-        <v>91258</v>
+        <v>8447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714298</v>
+        <v>714318</v>
       </c>
       <c r="R61" t="n">
-        <v>6395044</v>
+        <v>6395132</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7991,12 +7991,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
         <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>98377</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8238,55 +8238,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125798280</v>
+        <v>125800259</v>
       </c>
       <c r="B64" t="n">
-        <v>91258</v>
+        <v>98372</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714298</v>
+        <v>714261</v>
       </c>
       <c r="R64" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8313,19 +8306,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8340,22 +8323,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125800259</v>
+        <v>125799641</v>
       </c>
       <c r="B65" t="n">
-        <v>98368</v>
+        <v>95475</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8363,21 +8346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219847</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8387,7 +8370,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714261</v>
+        <v>714248</v>
       </c>
       <c r="R65" t="n">
         <v>6395081</v>
@@ -8442,55 +8425,62 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Erik Christiansson, Elvira Klang, Filippa Paperin, Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125799641</v>
+        <v>125798280</v>
       </c>
       <c r="B66" t="n">
-        <v>95471</v>
+        <v>91262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714248</v>
+        <v>714298</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8517,9 +8507,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8534,12 +8534,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8549,7 +8549,7 @@
         <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>110427</v>
+        <v>110440</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>125814124</v>
       </c>
       <c r="B68" t="n">
-        <v>56948</v>
+        <v>56952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8888,56 +8888,60 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B70" t="n">
-        <v>98368</v>
+        <v>57669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R70" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8964,19 +8968,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8991,22 +8985,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800859</v>
+        <v>125800830</v>
       </c>
       <c r="B71" t="n">
-        <v>98323</v>
+        <v>58134</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9014,27 +9008,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>102625</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9043,13 +9041,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R71" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S71" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9076,9 +9074,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9093,72 +9101,68 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800937</v>
+        <v>125798516</v>
       </c>
       <c r="B72" t="n">
-        <v>57665</v>
+        <v>98372</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100048</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R72" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9185,9 +9189,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9202,22 +9216,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Johanna Vanberg, Emilia Blixt</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800830</v>
+        <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>58130</v>
+        <v>98327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9225,31 +9239,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102625</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9258,13 +9268,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R73" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9291,19 +9301,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9318,12 +9318,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9449,7 +9449,7 @@
         <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>125808000</v>
       </c>
       <c r="B76" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9672,48 +9672,47 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797614</v>
+        <v>125808001</v>
       </c>
       <c r="B77" t="n">
-        <v>105931</v>
+        <v>85573</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R77" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9742,7 +9741,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9752,7 +9751,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9767,22 +9766,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808001</v>
+        <v>125797532</v>
       </c>
       <c r="B78" t="n">
-        <v>85569</v>
+        <v>8361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9790,36 +9789,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>258917</v>
+        <v>106540</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9873,44 +9873,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B79" t="n">
-        <v>8361</v>
+        <v>105944</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R79" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9980,12 +9980,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B46" t="n">
-        <v>91262</v>
+        <v>98372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,10 +6220,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6231,13 +6232,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R46" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6266,7 +6267,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6276,7 +6277,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6303,32 +6304,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B47" t="n">
-        <v>98372</v>
+        <v>91262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6338,11 +6339,10 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R47" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -9672,10 +9672,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125808001</v>
+        <v>125797532</v>
       </c>
       <c r="B77" t="n">
-        <v>85573</v>
+        <v>8361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9683,36 +9683,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>258917</v>
+        <v>106540</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R77" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9741,7 +9742,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9751,7 +9752,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9766,44 +9767,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B78" t="n">
-        <v>8361</v>
+        <v>105944</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9813,10 +9814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R78" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9848,7 +9849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9858,7 +9859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9873,60 +9874,59 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125797614</v>
+        <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>105944</v>
+        <v>85573</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R79" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9980,12 +9980,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6073,7 +6073,7 @@
         <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>125801883</v>
       </c>
       <c r="B46" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105296</v>
+        <v>105299</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6649,64 +6649,56 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B50" t="n">
-        <v>57938</v>
+        <v>98380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R50" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6735,7 +6727,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6745,7 +6737,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6760,68 +6752,76 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800012</v>
+        <v>125802957</v>
       </c>
       <c r="B51" t="n">
-        <v>98377</v>
+        <v>57938</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219864</v>
+        <v>103012</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714239</v>
+        <v>714254</v>
       </c>
       <c r="R51" t="n">
-        <v>6395154</v>
+        <v>6395049</v>
       </c>
       <c r="S51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,12 +6875,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800799</v>
+        <v>125798213</v>
       </c>
       <c r="B58" t="n">
-        <v>91262</v>
+        <v>8361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7552,30 +7552,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>106540</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7583,13 +7585,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714298</v>
+        <v>714315</v>
       </c>
       <c r="R58" t="n">
-        <v>6395044</v>
+        <v>6394992</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7618,7 +7620,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7628,7 +7630,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7655,43 +7657,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798213</v>
+        <v>125798048</v>
       </c>
       <c r="B59" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7699,13 +7701,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714315</v>
+        <v>714313</v>
       </c>
       <c r="R59" t="n">
-        <v>6394992</v>
+        <v>6395016</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7734,7 +7736,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7744,7 +7746,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7759,55 +7761,53 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125798048</v>
+        <v>125800799</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>91262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714313</v>
+        <v>714298</v>
       </c>
       <c r="R60" t="n">
-        <v>6395016</v>
+        <v>6395044</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7875,12 +7875,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -8003,47 +8003,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125797646</v>
+        <v>125799922</v>
       </c>
       <c r="B62" t="n">
-        <v>8361</v>
+        <v>98380</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106540</v>
+        <v>219864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8051,13 +8046,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714368</v>
+        <v>714240</v>
       </c>
       <c r="R62" t="n">
-        <v>6394946</v>
+        <v>6395123</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8086,7 +8081,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8096,7 +8091,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8111,54 +8106,59 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125799922</v>
+        <v>125797646</v>
       </c>
       <c r="B63" t="n">
-        <v>98377</v>
+        <v>8361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219864</v>
+        <v>106540</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714240</v>
+        <v>714368</v>
       </c>
       <c r="R63" t="n">
-        <v>6395123</v>
+        <v>6394946</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8226,22 +8226,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125800259</v>
+        <v>125797584</v>
       </c>
       <c r="B64" t="n">
-        <v>98372</v>
+        <v>110443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,37 +8249,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714261</v>
+        <v>714345</v>
       </c>
       <c r="R64" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8306,9 +8310,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8323,12 +8337,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8338,7 +8352,7 @@
         <v>125799641</v>
       </c>
       <c r="B65" t="n">
-        <v>95475</v>
+        <v>95478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8425,7 +8439,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erik Christiansson, Elvira Klang, Filippa Paperin, Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8546,10 +8560,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B67" t="n">
-        <v>110440</v>
+        <v>98375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8557,41 +8571,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R67" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S67" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8618,19 +8628,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8645,72 +8645,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B68" t="n">
-        <v>56952</v>
+        <v>8361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R68" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8739,7 +8732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8749,7 +8742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8764,65 +8757,72 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B69" t="n">
-        <v>8361</v>
+        <v>56952</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R69" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,72 +8876,68 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125800937</v>
+        <v>125798516</v>
       </c>
       <c r="B70" t="n">
-        <v>57669</v>
+        <v>98375</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100048</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R70" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8968,9 +8964,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8985,49 +8991,51 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800830</v>
+        <v>125800937</v>
       </c>
       <c r="B71" t="n">
-        <v>58134</v>
+        <v>57669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102625</v>
+        <v>100048</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9035,19 +9043,20 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R71" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9074,19 +9083,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9101,22 +9100,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125798516</v>
+        <v>125800830</v>
       </c>
       <c r="B72" t="n">
-        <v>98372</v>
+        <v>58134</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9124,45 +9123,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>102625</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714263</v>
+        <v>714267</v>
       </c>
       <c r="R72" t="n">
-        <v>6395090</v>
+        <v>6395077</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9216,12 +9216,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9231,7 +9231,7 @@
         <v>125800859</v>
       </c>
       <c r="B73" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9561,52 +9561,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125808000</v>
+        <v>125797532</v>
       </c>
       <c r="B76" t="n">
-        <v>79486</v>
+        <v>8361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1026</v>
+        <v>106540</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R76" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9635,7 +9631,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9645,7 +9641,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9660,44 +9656,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B77" t="n">
-        <v>8361</v>
+        <v>105947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9707,10 +9703,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R77" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9742,7 +9738,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9752,7 +9748,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9767,60 +9763,59 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797614</v>
+        <v>125808001</v>
       </c>
       <c r="B78" t="n">
-        <v>105944</v>
+        <v>85573</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R78" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9849,7 +9844,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9859,7 +9854,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9874,44 +9869,49 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808001</v>
+        <v>125808000</v>
       </c>
       <c r="B79" t="n">
-        <v>85573</v>
+        <v>79486</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>258917</v>
+        <v>1026</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6533,57 +6533,64 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125799723</v>
+        <v>125802957</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>57938</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>103012</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>714256</v>
+        <v>714254</v>
       </c>
       <c r="R49" t="n">
-        <v>6395124</v>
+        <v>6395049</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6612,7 +6619,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6622,7 +6629,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6637,22 +6644,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125800012</v>
+        <v>125799723</v>
       </c>
       <c r="B50" t="n">
-        <v>98380</v>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6660,31 +6667,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219864</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6692,13 +6700,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>714239</v>
+        <v>714256</v>
       </c>
       <c r="R50" t="n">
-        <v>6395154</v>
+        <v>6395124</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6727,7 +6735,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6737,7 +6745,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6764,64 +6772,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802957</v>
+        <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>57938</v>
+        <v>98380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103012</v>
+        <v>219864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>714254</v>
+        <v>714239</v>
       </c>
       <c r="R51" t="n">
-        <v>6395049</v>
+        <v>6395154</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,12 +6875,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elvira Klang, Alec Bailey, Elias Yngvesson, Elis Lewin, Emilia Blixt, Erik Christiansson, Filippa Paperin, Ivar Anderberg, Karin Andersson, Karl Soler Kinnerbäck, Malte Lindberg, Max Karlsson, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125797584</v>
+        <v>125800259</v>
       </c>
       <c r="B64" t="n">
-        <v>110443</v>
+        <v>98375</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,41 +8249,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714345</v>
+        <v>714261</v>
       </c>
       <c r="R64" t="n">
-        <v>6394926</v>
+        <v>6395081</v>
       </c>
       <c r="S64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8310,19 +8306,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8337,22 +8323,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125799641</v>
+        <v>125797584</v>
       </c>
       <c r="B65" t="n">
-        <v>95478</v>
+        <v>110443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8360,37 +8346,41 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2779</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714248</v>
+        <v>714345</v>
       </c>
       <c r="R65" t="n">
-        <v>6395081</v>
+        <v>6394926</v>
       </c>
       <c r="S65" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8417,9 +8407,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8434,67 +8434,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125798280</v>
+        <v>125799641</v>
       </c>
       <c r="B66" t="n">
-        <v>91262</v>
+        <v>95478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714298</v>
+        <v>714248</v>
       </c>
       <c r="R66" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8521,19 +8514,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8548,60 +8531,67 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125800259</v>
+        <v>125798280</v>
       </c>
       <c r="B67" t="n">
-        <v>98375</v>
+        <v>91262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714261</v>
+        <v>714298</v>
       </c>
       <c r="R67" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8628,9 +8618,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8645,65 +8645,72 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B68" t="n">
-        <v>8361</v>
+        <v>56952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R68" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8732,7 +8739,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8742,7 +8749,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8757,72 +8764,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B69" t="n">
-        <v>56952</v>
+        <v>8361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R69" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,12 +8876,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B74" t="n">
-        <v>8436</v>
+        <v>98375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9341,46 +9341,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R74" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9409,7 +9408,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9419,7 +9418,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9434,22 +9433,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B75" t="n">
-        <v>98375</v>
+        <v>8436</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9457,45 +9456,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R75" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S75" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,12 +9549,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6185,32 +6185,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125801883</v>
+        <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>98375</v>
+        <v>91262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6220,11 +6220,10 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6232,13 +6231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>714372</v>
+        <v>714304</v>
       </c>
       <c r="R46" t="n">
-        <v>6395100</v>
+        <v>6395005</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6277,7 +6276,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6304,32 +6303,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125798096</v>
+        <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>91262</v>
+        <v>98375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6339,10 +6338,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>714304</v>
+        <v>714372</v>
       </c>
       <c r="R47" t="n">
-        <v>6395005</v>
+        <v>6395100</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -8003,42 +8003,47 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125799922</v>
+        <v>125797646</v>
       </c>
       <c r="B62" t="n">
-        <v>98380</v>
+        <v>8361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219864</v>
+        <v>106540</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8046,13 +8051,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>714240</v>
+        <v>714368</v>
       </c>
       <c r="R62" t="n">
-        <v>6395123</v>
+        <v>6394946</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8081,7 +8086,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8091,7 +8096,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8106,59 +8111,54 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125797646</v>
+        <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>8361</v>
+        <v>98380</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106540</v>
+        <v>219864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8166,13 +8166,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>714368</v>
+        <v>714240</v>
       </c>
       <c r="R63" t="n">
-        <v>6394946</v>
+        <v>6395123</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8226,22 +8226,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125800259</v>
+        <v>125799641</v>
       </c>
       <c r="B64" t="n">
-        <v>98375</v>
+        <v>95478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>2779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714261</v>
+        <v>714248</v>
       </c>
       <c r="R64" t="n">
         <v>6395081</v>
@@ -8328,45 +8328,48 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125797584</v>
+        <v>125798280</v>
       </c>
       <c r="B65" t="n">
-        <v>110443</v>
+        <v>91262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8374,13 +8377,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714345</v>
+        <v>714298</v>
       </c>
       <c r="R65" t="n">
-        <v>6394926</v>
+        <v>6395026</v>
       </c>
       <c r="S65" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8409,7 +8412,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8419,7 +8422,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8446,10 +8449,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125799641</v>
+        <v>125800259</v>
       </c>
       <c r="B66" t="n">
-        <v>95478</v>
+        <v>98375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8457,21 +8460,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2779</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8481,7 +8484,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714248</v>
+        <v>714261</v>
       </c>
       <c r="R66" t="n">
         <v>6395081</v>
@@ -8536,48 +8539,45 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125798280</v>
+        <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>91262</v>
+        <v>110443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>714298</v>
+        <v>714345</v>
       </c>
       <c r="R67" t="n">
-        <v>6395026</v>
+        <v>6394926</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8657,60 +8657,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B68" t="n">
-        <v>56952</v>
+        <v>8361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R68" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8739,7 +8732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8749,7 +8742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8764,65 +8757,72 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B69" t="n">
-        <v>8361</v>
+        <v>56952</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R69" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,12 +8876,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125814167</v>
+        <v>125800866</v>
       </c>
       <c r="B74" t="n">
-        <v>98375</v>
+        <v>8436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9341,45 +9341,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219847</v>
+        <v>106554</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>714271</v>
+        <v>714279</v>
       </c>
       <c r="R74" t="n">
-        <v>6395065</v>
+        <v>6395120</v>
       </c>
       <c r="S74" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9408,7 +9409,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9418,7 +9419,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9433,22 +9434,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125800866</v>
+        <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>8436</v>
+        <v>98375</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9456,46 +9457,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106554</v>
+        <v>219847</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>714279</v>
+        <v>714271</v>
       </c>
       <c r="R75" t="n">
-        <v>6395120</v>
+        <v>6395065</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,22 +9549,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125797532</v>
+        <v>125808001</v>
       </c>
       <c r="B76" t="n">
-        <v>8361</v>
+        <v>85573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9572,37 +9572,36 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106540</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Svart askbastborre</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R76" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9631,7 +9630,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9641,7 +9640,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9656,44 +9655,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797614</v>
+        <v>125797532</v>
       </c>
       <c r="B77" t="n">
-        <v>105947</v>
+        <v>8361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
+        <v>106540</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9703,10 +9702,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714333</v>
+        <v>714342</v>
       </c>
       <c r="R77" t="n">
-        <v>6394948</v>
+        <v>6394935</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9738,7 +9737,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9748,7 +9747,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9763,59 +9762,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808001</v>
+        <v>125797614</v>
       </c>
       <c r="B78" t="n">
-        <v>85573</v>
+        <v>105947</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>258917</v>
+        <v>220785</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9869,12 +9869,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -8657,53 +8657,60 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B68" t="n">
-        <v>8361</v>
+        <v>56952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R68" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8732,7 +8739,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8742,7 +8749,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8757,72 +8764,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B69" t="n">
-        <v>56952</v>
+        <v>8361</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R69" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,12 +8876,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9561,10 +9561,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125808001</v>
+        <v>125797532</v>
       </c>
       <c r="B76" t="n">
-        <v>85573</v>
+        <v>8361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9572,36 +9572,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>258917</v>
+        <v>106540</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R76" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9630,7 +9631,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9640,7 +9641,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9655,44 +9656,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797532</v>
+        <v>125797614</v>
       </c>
       <c r="B77" t="n">
-        <v>8361</v>
+        <v>105947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106540</v>
+        <v>220785</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9702,10 +9703,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714342</v>
+        <v>714333</v>
       </c>
       <c r="R77" t="n">
-        <v>6394935</v>
+        <v>6394948</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9737,7 +9738,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9747,7 +9748,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9762,22 +9763,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125797614</v>
+        <v>125808000</v>
       </c>
       <c r="B78" t="n">
-        <v>105947</v>
+        <v>79486</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9785,37 +9786,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220785</v>
+        <v>1026</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R78" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9844,7 +9849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9854,7 +9859,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9869,49 +9874,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808000</v>
+        <v>125808001</v>
       </c>
       <c r="B79" t="n">
-        <v>79486</v>
+        <v>85573</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1026</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -6073,7 +6073,7 @@
         <v>125798802</v>
       </c>
       <c r="B45" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>125798096</v>
       </c>
       <c r="B46" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>125801883</v>
       </c>
       <c r="B47" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>125800049</v>
       </c>
       <c r="B48" t="n">
-        <v>105299</v>
+        <v>105308</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>125802957</v>
       </c>
       <c r="B49" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>125800012</v>
       </c>
       <c r="B51" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>125797549</v>
       </c>
       <c r="B52" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>125800687</v>
       </c>
       <c r="B53" t="n">
-        <v>58134</v>
+        <v>58137</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>125799309</v>
       </c>
       <c r="B54" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>125799607</v>
       </c>
       <c r="B55" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>125799057</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7541,43 +7541,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125798213</v>
+        <v>125801701</v>
       </c>
       <c r="B58" t="n">
-        <v>8361</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106540</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7585,13 +7585,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>714315</v>
+        <v>714318</v>
       </c>
       <c r="R58" t="n">
-        <v>6394992</v>
+        <v>6395132</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7645,55 +7645,55 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125798048</v>
+        <v>125798213</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>8361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>106540</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7701,13 +7701,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>714313</v>
+        <v>714315</v>
       </c>
       <c r="R59" t="n">
-        <v>6395016</v>
+        <v>6394992</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7761,53 +7761,55 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125800799</v>
+        <v>125798048</v>
       </c>
       <c r="B60" t="n">
-        <v>91262</v>
+        <v>8447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7815,13 +7817,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>714298</v>
+        <v>714313</v>
       </c>
       <c r="R60" t="n">
-        <v>6395044</v>
+        <v>6395016</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7850,7 +7852,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7860,7 +7862,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7875,55 +7877,53 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125801701</v>
+        <v>125800799</v>
       </c>
       <c r="B61" t="n">
-        <v>8447</v>
+        <v>91265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>714318</v>
+        <v>714298</v>
       </c>
       <c r="R61" t="n">
-        <v>6395132</v>
+        <v>6395044</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7991,12 +7991,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
         <v>125799922</v>
       </c>
       <c r="B63" t="n">
-        <v>98380</v>
+        <v>98389</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125799641</v>
+        <v>125800259</v>
       </c>
       <c r="B64" t="n">
-        <v>95478</v>
+        <v>98384</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2779</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>714248</v>
+        <v>714261</v>
       </c>
       <c r="R64" t="n">
         <v>6395081</v>
@@ -8328,62 +8328,55 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125798280</v>
+        <v>125799641</v>
       </c>
       <c r="B65" t="n">
-        <v>91262</v>
+        <v>95487</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>714298</v>
+        <v>714248</v>
       </c>
       <c r="R65" t="n">
-        <v>6395026</v>
+        <v>6395081</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8410,19 +8403,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8437,60 +8420,67 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Filippa Paperin, Elvira Klang, Erik Christiansson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125800259</v>
+        <v>125798280</v>
       </c>
       <c r="B66" t="n">
-        <v>98375</v>
+        <v>91265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219847</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>714261</v>
+        <v>714298</v>
       </c>
       <c r="R66" t="n">
-        <v>6395081</v>
+        <v>6395026</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8517,9 +8507,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8534,12 +8534,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8549,7 +8549,7 @@
         <v>125797584</v>
       </c>
       <c r="B67" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8657,60 +8657,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125814124</v>
+        <v>125798187</v>
       </c>
       <c r="B68" t="n">
-        <v>56952</v>
+        <v>8361</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100038</v>
+        <v>106540</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>714386</v>
+        <v>714301</v>
       </c>
       <c r="R68" t="n">
-        <v>6395050</v>
+        <v>6395029</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8739,7 +8732,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8749,7 +8742,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8764,65 +8757,72 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125798187</v>
+        <v>125814124</v>
       </c>
       <c r="B69" t="n">
-        <v>8361</v>
+        <v>56953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106540</v>
+        <v>100038</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>714301</v>
+        <v>714386</v>
       </c>
       <c r="R69" t="n">
-        <v>6395029</v>
+        <v>6395050</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8876,68 +8876,72 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Max Karlsson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125798516</v>
+        <v>125800937</v>
       </c>
       <c r="B70" t="n">
-        <v>98375</v>
+        <v>57670</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>714263</v>
+        <v>714265</v>
       </c>
       <c r="R70" t="n">
-        <v>6395090</v>
+        <v>6395124</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8964,19 +8968,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8991,51 +8985,49 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125800937</v>
+        <v>125800830</v>
       </c>
       <c r="B71" t="n">
-        <v>57669</v>
+        <v>58137</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100048</v>
+        <v>102625</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9043,20 +9035,19 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>714265</v>
+        <v>714267</v>
       </c>
       <c r="R71" t="n">
-        <v>6395124</v>
+        <v>6395077</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9083,9 +9074,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9100,22 +9101,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Alec Bailey, Elias Yngvesson, Filippa Paperin, Elvira Klang, Erik Christiansson, Malte Lindberg, Max Karlsson, Emilia Blixt, Johanna Vanberg</t>
+          <t>Malte Lindberg, Max Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125800830</v>
+        <v>125800859</v>
       </c>
       <c r="B72" t="n">
-        <v>58134</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9123,31 +9124,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102625</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9156,13 +9153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>714267</v>
+        <v>714265</v>
       </c>
       <c r="R72" t="n">
-        <v>6395077</v>
+        <v>6395124</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9189,19 +9186,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9216,22 +9203,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Max Karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125800859</v>
+        <v>125798516</v>
       </c>
       <c r="B73" t="n">
-        <v>98330</v>
+        <v>98384</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9239,42 +9226,45 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>714265</v>
+        <v>714263</v>
       </c>
       <c r="R73" t="n">
-        <v>6395124</v>
+        <v>6395090</v>
       </c>
       <c r="S73" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9301,9 +9291,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9318,12 +9318,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9449,7 +9449,7 @@
         <v>125814167</v>
       </c>
       <c r="B75" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9561,48 +9561,52 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125797532</v>
+        <v>125808000</v>
       </c>
       <c r="B76" t="n">
-        <v>8361</v>
+        <v>79489</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106540</v>
+        <v>1026</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>714342</v>
+        <v>714264</v>
       </c>
       <c r="R76" t="n">
-        <v>6394935</v>
+        <v>6395004</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9631,7 +9635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9641,7 +9645,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9656,60 +9660,59 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elis Lewin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125797614</v>
+        <v>125808001</v>
       </c>
       <c r="B77" t="n">
-        <v>105947</v>
+        <v>85576</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
+          <t>Stora sojdeby, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>714333</v>
+        <v>714264</v>
       </c>
       <c r="R77" t="n">
-        <v>6394948</v>
+        <v>6395004</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9738,7 +9741,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9748,7 +9751,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9763,64 +9766,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125808000</v>
+        <v>125797532</v>
       </c>
       <c r="B78" t="n">
-        <v>79486</v>
+        <v>8361</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1026</v>
+        <v>106540</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>714264</v>
+        <v>714342</v>
       </c>
       <c r="R78" t="n">
-        <v>6395004</v>
+        <v>6394935</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9849,7 +9848,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9859,7 +9858,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9874,59 +9873,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elis Lewin, Elvira Klang, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125808001</v>
+        <v>125797614</v>
       </c>
       <c r="B79" t="n">
-        <v>85573</v>
+        <v>105956</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>258917</v>
+        <v>220785</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stora sojdeby, Gtl</t>
+          <t>Änge gamla tomt, Änge gamla tomt, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>714264</v>
+        <v>714333</v>
       </c>
       <c r="R79" t="n">
-        <v>6395004</v>
+        <v>6394948</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9980,12 +9980,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Filippa Paperin, Elias Yngvesson, Elis Lewin, Elvira Klang, Erik Christiansson, Ivar Anderberg, Karin Andersson, Malte Lindberg, Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
         <v>125800234</v>
       </c>
       <c r="B81" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>126147610</v>
       </c>
       <c r="B82" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>125801401</v>
       </c>
       <c r="B83" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>125797737</v>
       </c>
       <c r="B84" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>126917264</v>
       </c>
       <c r="B85" t="n">
-        <v>80669</v>
+        <v>80700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>126917264</v>
       </c>
       <c r="B85" t="n">
-        <v>80700</v>
+        <v>80703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>126917264</v>
       </c>
       <c r="B85" t="n">
-        <v>80703</v>
+        <v>80707</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>126917264</v>
       </c>
       <c r="B85" t="n">
-        <v>80707</v>
+        <v>80709</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 25218-2021 artfynd.xlsx
+++ b/artfynd/A 25218-2021 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>126917264</v>
       </c>
       <c r="B85" t="n">
-        <v>80709</v>
+        <v>80700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
